--- a/output/pdf_financials_xlsx/TLT.xlsx
+++ b/output/pdf_financials_xlsx/TLT.xlsx
@@ -1059,58 +1059,58 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.009835</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005869</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005655</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.011665</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.013119</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008481000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008423999999999999</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.037171</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015429</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006614</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.018626</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.033603</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.103686</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022662</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.030661</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.049811</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.066451</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07929600000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2082,58 +2082,58 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.111675</v>
+        <v>-1.10184</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.241578</v>
+        <v>-0.235709</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.16835</v>
+        <v>-1.162695</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.453974</v>
+        <v>-1.442309</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.509569</v>
+        <v>-1.49645</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.152209</v>
+        <v>-1.143728</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.587542</v>
+        <v>-2.579118</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.208145</v>
+        <v>-5.170974</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.921248</v>
+        <v>-4.905819</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-6.093596</v>
+        <v>-6.086982</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-3.356877</v>
+        <v>-3.338251</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-7.413914</v>
+        <v>-7.380311</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.59854</v>
+        <v>-5.494854</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.411061</v>
+        <v>-4.388399</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-5.235302</v>
+        <v>-5.204641</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-4.570879</v>
+        <v>-4.521068</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-4.256114</v>
+        <v>-4.189663</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-4.120817</v>
+        <v>-4.041521</v>
       </c>
     </row>
     <row r="28">
@@ -2204,58 +2204,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.964053</v>
+        <v>-0.954218</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.099179</v>
+        <v>-0.09331</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.099722</v>
+        <v>-1.094067</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.436133</v>
+        <v>-1.424468</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.491119</v>
+        <v>-1.478</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.13417</v>
+        <v>-1.125689</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.569504</v>
+        <v>-2.56108</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.187178</v>
+        <v>-5.150007</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.901928</v>
+        <v>-4.886499</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.075558</v>
+        <v>-6.068944</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-3.338938</v>
+        <v>-3.320312</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-7.413914</v>
+        <v>-7.380311</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.59854</v>
+        <v>-5.494854</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.411061</v>
+        <v>-4.388399</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-5.235302</v>
+        <v>-5.204641</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-4.570879</v>
+        <v>-4.521068</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-4.256114</v>
+        <v>-4.189663</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-4.120817</v>
+        <v>-4.041521</v>
       </c>
     </row>
     <row r="30">
@@ -2265,58 +2265,58 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-44.45896096265884</v>
+        <v>-44.00540303475678</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-4.202758220314384</v>
+        <v>-3.954056499234063</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-53.89375443816995</v>
+        <v>-53.61662150698566</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-70.84814544033767</v>
+        <v>-70.27268090010251</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-81.73591922000227</v>
+        <v>-81.01679920057578</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-94.22990644887922</v>
+        <v>-93.52528206576827</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-186.1144832261822</v>
+        <v>-185.5043155024902</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-266.6592297323834</v>
+        <v>-264.7483660164319</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-255.4560363709701</v>
+        <v>-254.6519790316605</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-259.3612487129179</v>
+        <v>-259.0789017582864</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-192.548982971872</v>
+        <v>-191.4748637888162</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-769.037530172159</v>
+        <v>-765.551926194776</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-602.5624191440952</v>
+        <v>-591.4028512940174</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-565.0562806719095</v>
+        <v>-562.1532817261711</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-459.8142053753439</v>
+        <v>-457.121263621265</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-427.0624222769729</v>
+        <v>-422.4085239094952</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-411.8430741868592</v>
+        <v>-405.4129400027675</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-504.7126158036813</v>
+        <v>-495.0005389066075</v>
       </c>
     </row>
     <row r="31">
@@ -2464,13 +2464,13 @@
         <v>0.174401</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.04306</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.021975</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.768329</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.922454</v>
@@ -2586,13 +2586,13 @@
         <v>0.174401</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.04306</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.021975</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.768329</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.922454</v>
@@ -3318,13 +3318,13 @@
         <v>1.063534</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.082096</v>
+        <v>0.039036</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.048689</v>
+        <v>0.026714</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.826401</v>
+        <v>0.058072</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.574861</v>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -39656,7 +39656,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" s="5" t="n">
@@ -39746,7 +39746,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -42806,7 +42806,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -42902,7 +42902,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -44954,7 +44954,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -46110,7 +46110,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E358" s="5" t="n">

--- a/output/pdf_financials_xlsx/TLT.xlsx
+++ b/output/pdf_financials_xlsx/TLT.xlsx
@@ -6537,13 +6537,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.147622</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.142399</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.06862799999999999</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -7443,28 +7443,28 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.012525</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.004599</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.000836</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.0016</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -26906,7 +26906,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -28684,7 +28688,11 @@
           <t>Proceeds on disposal of property and equipment 6</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -29712,7 +29720,11 @@
           <t>Proceeds on sale of property and equipment 8</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -34534,7 +34546,11 @@
           <t>Proceeds on disposal of property and equipment 8</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -35906,7 +35922,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E259" s="5" t="n">
@@ -47048,7 +47064,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E367" s="5" t="n">
